--- a/TASK2/Scenariji/SC06_EvidencijaDolazakaQR.xlsx
+++ b/TASK2/Scenariji/SC06_EvidencijaDolazakaQR.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clan skenira QR kod na ulazu u teretanu. Sistem validira QR kod i evidentira dolazak.</t>
+          <t>Član skenira QR kod na ulazu u teretanu. Sistem validira QR kod i evidentira dolazak.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generisanje QR koda za svakog registrovanog clana; Evidentiranje svakog dolaska clana sa tacnim vremenom</t>
+          <t>Generisanje QR koda za svakog registrovanog člana; Evidentiranje svakog dolaska člana sa tačnim vremenom</t>
         </is>
       </c>
     </row>
@@ -497,31 +497,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>QR citac je aktivan. Clan ima generiran QR kod.</t>
+          <t>QR čitač je aktivan. Član ima generiran QR kod.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Dolazak je evidentiran, clan je usao u teretanu.</t>
+          <t>Dolazak je evidentiran, član je usao u teretanu.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ulaz je odbijen zbog neaktivne clanarine ili nevalidnog QR koda.</t>
+          <t>Ulaz je odbijen zbog neaktivne članarine ili nevalidnog QR koda.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>QR citac, Sistem</t>
+          <t>QR čitač, Sistem</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Clan skenira QR kod, sistem validira i evidentira dolazak.</t>
+          <t>Član skenira QR kod, sistem validira i evidentira dolazak.</t>
         </is>
       </c>
     </row>
@@ -569,10 +569,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Neaktivna clanarina, Nevalidan QR kod, Rucni unos koda</t>
-        </is>
-      </c>
-    </row>
+          <t>Neaktivna članarina, Nevalidan QR kod, Rucni unos koda</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -583,12 +584,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>QR citac</t>
+          <t>QR čitač</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -600,35 +601,35 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1. Clan skenira svoj QR kod na ulazu u teretanu</t>
+          <t>1. Član skenira svoj QR kod na ulazu u teretanu</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2. QR citac prima QR kod</t>
+          <t>2. QR čitač prima QR kod</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3. Sistem validira QR kod i identificira clana</t>
+          <t>3. Sistem validira QR kod i identificira člana</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4. Sistem provjerava da li clan ima aktivnu clanarinu</t>
+          <t>4. Sistem provjerava da li član ima aktivnu članarinu</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5. Sistem evidentira dolazak sa tacnim vremenom</t>
+          <t>5. Sistem evidentira dolazak sa tačnim vremenom</t>
         </is>
       </c>
     </row>
@@ -642,26 +643,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>7. Clanu je omogucen ulaz u teretanu</t>
-        </is>
-      </c>
-    </row>
+          <t>7. Clanu je omogućen ulaz u teretanu</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Neaktivna clanarina</t>
+          <t>Alternativni Tok - Neaktivna članarina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>QR citac</t>
+          <t>QR čitač</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -673,7 +675,7 @@
     <row r="24">
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4a. Sistem detektuje da clan nema aktivnu clanarinu</t>
+          <t>4a. Sistem detektuje da član nema aktivnu članarinu</t>
         </is>
       </c>
     </row>
@@ -694,10 +696,11 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>4d. Clan mora kupiti/obnoviti clanarinu</t>
-        </is>
-      </c>
-    </row>
+          <t>4d. Član mora kupiti/obnoviti članarinu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
@@ -708,12 +711,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>QR citac</t>
+          <t>QR čitač</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -725,7 +728,7 @@
     <row r="31">
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3a. Sistem ne moze validirati QR kod</t>
+          <t>3a. Sistem ne može validirati QR kod</t>
         </is>
       </c>
     </row>
@@ -739,7 +742,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>3c. Clan pokusava ponovo ili koristi rucni unos</t>
+          <t>3c. Član pokušava ponovo ili koristi ručni unos</t>
         </is>
       </c>
     </row>
